--- a/Data/ModelResponse/WithTranscription/transcription_evaluation/evaluation_summary.xlsx
+++ b/Data/ModelResponse/WithTranscription/transcription_evaluation/evaluation_summary.xlsx
@@ -497,37 +497,37 @@
         <v>19200</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>19200</v>
       </c>
       <c r="D2" t="n">
-        <v>16585</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06901041666666667</v>
+        <v>0.4975</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5310394815383304</v>
+        <v>0.4921922302094915</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0693401879756701</v>
+        <v>0.4998768634922217</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1090704979694186</v>
+        <v>0.3355932341508326</v>
       </c>
       <c r="J2" t="n">
-        <v>1320</v>
+        <v>9515</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="L2" t="n">
-        <v>1286</v>
+        <v>9609</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -621,37 +621,37 @@
         <v>800</v>
       </c>
       <c r="C2" t="n">
-        <v>106</v>
+        <v>800</v>
       </c>
       <c r="D2" t="n">
-        <v>694</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.065</v>
+        <v>0.485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.7421777221526908</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06718346253229975</v>
+        <v>0.5012106537530266</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1054766734279919</v>
+        <v>0.3287223729338254</v>
       </c>
       <c r="J2" t="n">
-        <v>52</v>
+        <v>387</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>54</v>
+        <v>412</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -664,34 +664,34 @@
         <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="D3" t="n">
-        <v>693</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2616822429906542</v>
+        <v>0.2525</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06930693069306931</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1095890410958904</v>
+        <v>0.3355481727574751</v>
       </c>
       <c r="J3" t="n">
-        <v>56</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>51</v>
+        <v>396</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -707,37 +707,37 @@
         <v>1600</v>
       </c>
       <c r="C4" t="n">
-        <v>211</v>
+        <v>1600</v>
       </c>
       <c r="D4" t="n">
-        <v>1389</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.059375</v>
+        <v>0.5125</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4746376811594203</v>
+        <v>0.501036084315827</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0579219430889097</v>
+        <v>0.5001133593616851</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09302120448638629</v>
+        <v>0.3625576149847994</v>
       </c>
       <c r="J4" t="n">
-        <v>93</v>
+        <v>798</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L4" t="n">
-        <v>114</v>
+        <v>757</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -750,37 +750,37 @@
         <v>1600</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>1600</v>
       </c>
       <c r="D5" t="n">
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06375</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2318181818181818</v>
+        <v>0.4656981436642453</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06335403726708075</v>
+        <v>0.4994023204031408</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09951219512195121</v>
+        <v>0.3377690053431892</v>
       </c>
       <c r="J5" t="n">
-        <v>102</v>
+        <v>801</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>118</v>
+        <v>792</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -793,37 +793,37 @@
         <v>1600</v>
       </c>
       <c r="C6" t="n">
-        <v>211</v>
+        <v>1600</v>
       </c>
       <c r="D6" t="n">
-        <v>1389</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0725</v>
+        <v>0.511875</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7738095238095238</v>
+        <v>0.4705908845253107</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07067838932764607</v>
+        <v>0.4989789839561323</v>
       </c>
       <c r="I6" t="n">
-        <v>0.112824243328608</v>
+        <v>0.345331056801018</v>
       </c>
       <c r="J6" t="n">
-        <v>115</v>
+        <v>813</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>95</v>
+        <v>773</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -836,34 +836,34 @@
         <v>1600</v>
       </c>
       <c r="C7" t="n">
-        <v>220</v>
+        <v>1600</v>
       </c>
       <c r="D7" t="n">
-        <v>1380</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06625</v>
+        <v>0.461875</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2409090909090909</v>
+        <v>0.2310819262038774</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07162162162162163</v>
+        <v>0.4993243243243243</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1104166666666667</v>
+        <v>0.3159469858914066</v>
       </c>
       <c r="J7" t="n">
-        <v>106</v>
+        <v>739</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>114</v>
+        <v>860</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -879,37 +879,37 @@
         <v>1600</v>
       </c>
       <c r="C8" t="n">
-        <v>216</v>
+        <v>1600</v>
       </c>
       <c r="D8" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.074375</v>
+        <v>0.4825</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7733644859813085</v>
+        <v>0.5978835978835979</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07727619128097032</v>
+        <v>0.5017080334690058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1214243581461069</v>
+        <v>0.3306913965956604</v>
       </c>
       <c r="J8" t="n">
-        <v>117</v>
+        <v>767</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>97</v>
+        <v>826</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -922,34 +922,34 @@
         <v>1600</v>
       </c>
       <c r="C9" t="n">
-        <v>227</v>
+        <v>1600</v>
       </c>
       <c r="D9" t="n">
-        <v>1373</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.51375</v>
       </c>
       <c r="G9" t="n">
-        <v>0.247787610619469</v>
+        <v>0.256875</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06812652068126521</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1068702290076336</v>
+        <v>0.3393889347646574</v>
       </c>
       <c r="J9" t="n">
-        <v>112</v>
+        <v>822</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>114</v>
+        <v>778</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -965,34 +965,34 @@
         <v>1600</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>1600</v>
       </c>
       <c r="D10" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.066875</v>
+        <v>0.501875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2476851851851852</v>
+        <v>0.2510944340212633</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06654228855721393</v>
+        <v>0.4993781094527363</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1049019607843137</v>
+        <v>0.3341656263004578</v>
       </c>
       <c r="J10" t="n">
-        <v>107</v>
+        <v>803</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>109</v>
+        <v>796</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1008,34 +1008,34 @@
         <v>1600</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>1600</v>
       </c>
       <c r="D11" t="n">
-        <v>1375</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07875</v>
+        <v>0.5075</v>
       </c>
       <c r="G11" t="n">
-        <v>0.28</v>
+        <v>0.25375</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07758620689655173</v>
+        <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1215043394406943</v>
+        <v>0.3366500829187397</v>
       </c>
       <c r="J11" t="n">
-        <v>126</v>
+        <v>812</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>99</v>
+        <v>788</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1051,34 +1051,34 @@
         <v>1600</v>
       </c>
       <c r="C12" t="n">
-        <v>215</v>
+        <v>1600</v>
       </c>
       <c r="D12" t="n">
-        <v>1385</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.074375</v>
+        <v>0.4925</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2767441860465116</v>
+        <v>0.24625</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07550761421319797</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1186440677966102</v>
+        <v>0.3299832495812395</v>
       </c>
       <c r="J12" t="n">
-        <v>119</v>
+        <v>788</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>96</v>
+        <v>812</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1094,34 +1094,34 @@
         <v>1600</v>
       </c>
       <c r="C13" t="n">
-        <v>222</v>
+        <v>1600</v>
       </c>
       <c r="D13" t="n">
-        <v>1378</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06375</v>
+        <v>0.508125</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2297297297297297</v>
+        <v>0.2540625</v>
       </c>
       <c r="H13" t="n">
-        <v>0.06273062730627306</v>
+        <v>0.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09855072463768115</v>
+        <v>0.3369249896394529</v>
       </c>
       <c r="J13" t="n">
-        <v>102</v>
+        <v>813</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>120</v>
+        <v>787</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1137,34 +1137,34 @@
         <v>1600</v>
       </c>
       <c r="C14" t="n">
-        <v>219</v>
+        <v>1600</v>
       </c>
       <c r="D14" t="n">
-        <v>1381</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.07062499999999999</v>
+        <v>0.48</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2591743119266055</v>
+        <v>0.24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07356770833333333</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.114604462474645</v>
+        <v>0.3243243243243243</v>
       </c>
       <c r="J14" t="n">
-        <v>113</v>
+        <v>768</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>105</v>
+        <v>832</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1261,34 +1261,34 @@
         <v>192</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D2" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.078125</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2317708333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08426966292134831</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.3167259786476868</v>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -1304,37 +1304,37 @@
         <v>192</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D3" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>0.28</v>
+        <v>0.7447368421052631</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07526881720430108</v>
+        <v>0.5101010101010101</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1186440677966102</v>
+        <v>0.3484238883252283</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1347,34 +1347,34 @@
         <v>192</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D4" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.078125</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25</v>
+        <v>0.2853403141361257</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.4954545454545455</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.3621262458471761</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1390,37 +1390,37 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D5" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1923076923076923</v>
+        <v>0.7539267015706806</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05154639175257732</v>
+        <v>0.5052631578947369</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08130081300813007</v>
+        <v>0.3472222222222223</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1433,37 +1433,37 @@
         <v>192</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D6" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09375</v>
+        <v>0.53125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.2670157068062827</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08814224937275009</v>
+        <v>0.4951456310679612</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1428940568475452</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1476,34 +1476,34 @@
         <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D7" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>0.25</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07446808510638298</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1147540983606557</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1519,37 +1519,37 @@
         <v>192</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D8" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.484375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.7408376963350786</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05978260869565218</v>
+        <v>0.505</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09243697478991597</v>
+        <v>0.3349893293216247</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1562,34 +1562,34 @@
         <v>192</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D9" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09375</v>
+        <v>0.546875</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8148148148148149</v>
+        <v>0.7722513089005236</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08741258741258741</v>
+        <v>0.5056818181818182</v>
       </c>
       <c r="I9" t="n">
-        <v>0.141006947422592</v>
+        <v>0.3637783279375357</v>
       </c>
       <c r="J9" t="n">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1605,34 +1605,34 @@
         <v>192</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.078125</v>
+        <v>0.546875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.274869109947644</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07075471698113207</v>
+        <v>0.4952830188679245</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.3535353535353535</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1648,37 +1648,37 @@
         <v>192</v>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.5846560846560847</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08943089430894308</v>
+        <v>0.3535353535353536</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1691,34 +1691,34 @@
         <v>192</v>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.2486910994764398</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>0.064</v>
+        <v>0.3310104529616725</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1734,34 +1734,34 @@
         <v>192</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D13" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03125</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03125</v>
+        <v>0.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04958677685950413</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1777,34 +1777,34 @@
         <v>192</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D14" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="G14" t="n">
-        <v>0.26</v>
+        <v>0.2827225130890053</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05963302752293578</v>
+        <v>0.4954128440366973</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09701492537313434</v>
+        <v>0.36</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1820,34 +1820,34 @@
         <v>192</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D15" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09375</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>0.36</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09574468085106383</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1512605042016807</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1863,37 +1863,37 @@
         <v>192</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D16" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.25</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07222222222222222</v>
+        <v>0.5098039215686274</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1120689655172414</v>
+        <v>0.3406593406593407</v>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1906,34 +1906,34 @@
         <v>192</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D17" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0625</v>
+        <v>0.421875</v>
       </c>
       <c r="G17" t="n">
-        <v>0.24</v>
+        <v>0.2109375</v>
       </c>
       <c r="H17" t="n">
-        <v>0.07407407407407407</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.2967032967032967</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1949,34 +1949,34 @@
         <v>192</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D18" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09375</v>
+        <v>0.546875</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.2734375</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.5</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1343283582089552</v>
+        <v>0.3535353535353535</v>
       </c>
       <c r="J18" t="n">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1992,34 +1992,34 @@
         <v>192</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D19" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>0.26</v>
+        <v>0.2526041666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06701030927835051</v>
+        <v>0.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1065573770491803</v>
+        <v>0.3356401384083045</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2035,37 +2035,37 @@
         <v>192</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D20" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.078125</v>
+        <v>0.4375</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.7172774869109948</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09036144578313253</v>
+        <v>0.5045871559633027</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1376146788990826</v>
+        <v>0.3120106171201062</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2078,34 +2078,34 @@
         <v>192</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D21" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G21" t="n">
-        <v>0.28</v>
+        <v>0.2578125</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2121,34 +2121,34 @@
         <v>192</v>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D22" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>0.25</v>
+        <v>0.2094240837696335</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08024691358024691</v>
+        <v>0.4938271604938271</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1214953271028037</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2164,34 +2164,34 @@
         <v>192</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D23" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0625</v>
+        <v>0.4375</v>
       </c>
       <c r="G23" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="J23" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2207,34 +2207,34 @@
         <v>192</v>
       </c>
       <c r="C24" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D24" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.078125</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08522727272727272</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1293103448275862</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2250,37 +2250,37 @@
         <v>192</v>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D25" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.7591623036649215</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08080808080808081</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="I25" t="n">
-        <v>0.128</v>
+        <v>0.352017608217168</v>
       </c>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2293,34 +2293,34 @@
         <v>192</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D26" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.453125</v>
       </c>
       <c r="G26" t="n">
-        <v>0.26</v>
+        <v>0.2265625</v>
       </c>
       <c r="H26" t="n">
-        <v>0.07471264367816093</v>
+        <v>0.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1160714285714286</v>
+        <v>0.3118279569892473</v>
       </c>
       <c r="J26" t="n">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2336,34 +2336,34 @@
         <v>192</v>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D27" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2630208333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06435643564356436</v>
+        <v>0.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1015625</v>
+        <v>0.3447098976109215</v>
       </c>
       <c r="J27" t="n">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2379,37 +2379,37 @@
         <v>192</v>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D28" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2115384615384615</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="n">
-        <v>0.05789473684210526</v>
+        <v>0.5103092783505154</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3535353535353535</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2422,34 +2422,34 @@
         <v>192</v>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D29" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.46875</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2115384615384615</v>
+        <v>0.234375</v>
       </c>
       <c r="H29" t="n">
-        <v>0.06111111111111111</v>
+        <v>0.5</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09482758620689656</v>
+        <v>0.3191489361702128</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2465,34 +2465,34 @@
         <v>192</v>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D30" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.256544502617801</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08080808080808081</v>
+        <v>0.494949494949495</v>
       </c>
       <c r="I30" t="n">
-        <v>0.128</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="J30" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2508,34 +2508,34 @@
         <v>192</v>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D31" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="H31" t="n">
-        <v>0.07065217391304347</v>
+        <v>0.5</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1092436974789916</v>
+        <v>0.323943661971831</v>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2551,34 +2551,34 @@
         <v>192</v>
       </c>
       <c r="C32" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D32" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2115384615384615</v>
+        <v>0.2303664921465969</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06179775280898876</v>
+        <v>0.4943820224719101</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09565217391304347</v>
+        <v>0.3142857142857142</v>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2594,34 +2594,34 @@
         <v>192</v>
       </c>
       <c r="C33" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D33" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="H33" t="n">
-        <v>0.06914893617021277</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1074380165289256</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="J33" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2637,34 +2637,34 @@
         <v>192</v>
       </c>
       <c r="C34" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D34" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0625</v>
+        <v>0.484375</v>
       </c>
       <c r="G34" t="n">
-        <v>0.24</v>
+        <v>0.2421875</v>
       </c>
       <c r="H34" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1016949152542373</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="J34" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2680,37 +2680,37 @@
         <v>192</v>
       </c>
       <c r="C35" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D35" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.7408376963350786</v>
       </c>
       <c r="H35" t="n">
-        <v>0.07065217391304347</v>
+        <v>0.505</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1092436974789916</v>
+        <v>0.3349893293216247</v>
       </c>
       <c r="J35" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2723,37 +2723,37 @@
         <v>192</v>
       </c>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D36" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4427083333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>0.28</v>
+        <v>0.7198952879581152</v>
       </c>
       <c r="H36" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5046296296296297</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1284403669724771</v>
+        <v>0.314628857381151</v>
       </c>
       <c r="J36" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2766,34 +2766,34 @@
         <v>192</v>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D37" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.515625</v>
       </c>
       <c r="G37" t="n">
-        <v>0.26</v>
+        <v>0.2591623036649215</v>
       </c>
       <c r="H37" t="n">
-        <v>0.065</v>
+        <v>0.495</v>
       </c>
       <c r="I37" t="n">
-        <v>0.104</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="J37" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2809,34 +2809,34 @@
         <v>192</v>
       </c>
       <c r="C38" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D38" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.2539267015706806</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05612244897959184</v>
+        <v>0.4948979591836735</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09016393442622951</v>
+        <v>0.3356401384083045</v>
       </c>
       <c r="J38" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2852,34 +2852,34 @@
         <v>192</v>
       </c>
       <c r="C39" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D39" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0625</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2172774869109948</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1081081081081081</v>
+        <v>0.3018181818181818</v>
       </c>
       <c r="J39" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2895,37 +2895,37 @@
         <v>192</v>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D40" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G40" t="n">
-        <v>0.28</v>
+        <v>0.756544502617801</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.5053191489361702</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1138211382113821</v>
+        <v>0.3496266618102349</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2938,34 +2938,34 @@
         <v>192</v>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D41" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2722513089005236</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1085271317829457</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="J41" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2981,37 +2981,37 @@
         <v>192</v>
       </c>
       <c r="C42" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D42" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.3968253968253968</v>
       </c>
       <c r="H42" t="n">
-        <v>0.07303370786516854</v>
+        <v>0.493618413875859</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1120689655172414</v>
+        <v>0.3223836025519207</v>
       </c>
       <c r="J42" t="n">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3024,37 +3024,37 @@
         <v>192</v>
       </c>
       <c r="C43" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D43" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.3513368983957219</v>
       </c>
       <c r="H43" t="n">
-        <v>0.05612244897959184</v>
+        <v>0.484910985670864</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.3399255715045189</v>
       </c>
       <c r="J43" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3067,37 +3067,37 @@
         <v>192</v>
       </c>
       <c r="C44" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D44" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.578125</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.5398936170212766</v>
       </c>
       <c r="H44" t="n">
-        <v>0.07657657657657657</v>
+        <v>0.5033366700033366</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1223021582733813</v>
+        <v>0.3880779067479835</v>
       </c>
       <c r="J44" t="n">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -3110,34 +3110,34 @@
         <v>192</v>
       </c>
       <c r="C45" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D45" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.046875</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.2473958333333333</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04736842105263158</v>
+        <v>0.5</v>
       </c>
       <c r="I45" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.3310104529616725</v>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3153,34 +3153,34 @@
         <v>192</v>
       </c>
       <c r="C46" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D46" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.53125</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.265625</v>
       </c>
       <c r="H46" t="n">
-        <v>0.06862745098039216</v>
+        <v>0.5</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="J46" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3196,37 +3196,37 @@
         <v>192</v>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D47" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.7591623036649215</v>
       </c>
       <c r="H47" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="I47" t="n">
-        <v>0.096</v>
+        <v>0.352017608217168</v>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3239,34 +3239,34 @@
         <v>192</v>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D48" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0625</v>
+        <v>0.484375</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2421875</v>
       </c>
       <c r="H48" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1008403361344538</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3282,34 +3282,34 @@
         <v>192</v>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D49" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.453125</v>
       </c>
       <c r="G49" t="n">
-        <v>0.26</v>
+        <v>0.2265625</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07471264367816093</v>
+        <v>0.5</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1160714285714286</v>
+        <v>0.3118279569892473</v>
       </c>
       <c r="J49" t="n">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3325,34 +3325,34 @@
         <v>192</v>
       </c>
       <c r="C50" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D50" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="H50" t="n">
-        <v>0.07386363636363637</v>
+        <v>0.5</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1130434782608696</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3368,37 +3368,37 @@
         <v>192</v>
       </c>
       <c r="C51" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D51" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7307692307692308</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="H51" t="n">
-        <v>0.07298951048951048</v>
+        <v>0.5</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1147869674185464</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="J51" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3411,34 +3411,34 @@
         <v>192</v>
       </c>
       <c r="C52" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D52" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0625</v>
+        <v>0.484375</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2421875</v>
       </c>
       <c r="H52" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.5</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1008403361344538</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="J52" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -3454,34 +3454,34 @@
         <v>192</v>
       </c>
       <c r="C53" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D53" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0625</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2473958333333333</v>
       </c>
       <c r="H53" t="n">
-        <v>0.06315789473684211</v>
+        <v>0.5</v>
       </c>
       <c r="I53" t="n">
-        <v>0.09917355371900827</v>
+        <v>0.3310104529616725</v>
       </c>
       <c r="J53" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3497,34 +3497,34 @@
         <v>192</v>
       </c>
       <c r="C54" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D54" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G54" t="n">
-        <v>0.25</v>
+        <v>0.256544502617801</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.494949494949495</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1102362204724409</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="J54" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3540,34 +3540,34 @@
         <v>192</v>
       </c>
       <c r="C55" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D55" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.46875</v>
       </c>
       <c r="G55" t="n">
-        <v>0.22</v>
+        <v>0.234375</v>
       </c>
       <c r="H55" t="n">
-        <v>0.06111111111111111</v>
+        <v>0.5</v>
       </c>
       <c r="I55" t="n">
-        <v>0.09565217391304348</v>
+        <v>0.3191489361702128</v>
       </c>
       <c r="J55" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -3583,34 +3583,34 @@
         <v>192</v>
       </c>
       <c r="C56" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D56" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G56" t="n">
-        <v>0.16</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.5</v>
       </c>
       <c r="I56" t="n">
-        <v>0.06722689075630252</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="J56" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -3626,34 +3626,34 @@
         <v>192</v>
       </c>
       <c r="C57" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D57" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2758620689655172</v>
+        <v>0.2473958333333333</v>
       </c>
       <c r="H57" t="n">
-        <v>0.08421052631578947</v>
+        <v>0.5</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.3310104529616725</v>
       </c>
       <c r="J57" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -3669,34 +3669,34 @@
         <v>192</v>
       </c>
       <c r="C58" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D58" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.2369791666666667</v>
       </c>
       <c r="H58" t="n">
-        <v>0.05494505494505494</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0847457627118644</v>
+        <v>0.3215547703180212</v>
       </c>
       <c r="J58" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -3712,37 +3712,37 @@
         <v>192</v>
       </c>
       <c r="C59" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D59" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.078125</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.7303664921465969</v>
       </c>
       <c r="H59" t="n">
-        <v>0.08522727272727272</v>
+        <v>0.5048076923076923</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.3249359959037378</v>
       </c>
       <c r="J59" t="n">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3755,34 +3755,34 @@
         <v>192</v>
       </c>
       <c r="C60" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D60" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.078125</v>
+        <v>0.578125</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.2890625</v>
       </c>
       <c r="H60" t="n">
-        <v>0.06756756756756757</v>
+        <v>0.5</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1079136690647482</v>
+        <v>0.3663366336633663</v>
       </c>
       <c r="J60" t="n">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -3798,34 +3798,34 @@
         <v>192</v>
       </c>
       <c r="C61" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D61" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.2552083333333333</v>
       </c>
       <c r="H61" t="n">
-        <v>0.09183673469387756</v>
+        <v>0.5</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="J61" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3841,37 +3841,37 @@
         <v>192</v>
       </c>
       <c r="C62" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D62" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.7774869109947644</v>
       </c>
       <c r="H62" t="n">
-        <v>0.06132075471698113</v>
+        <v>0.5058139534883721</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1</v>
+        <v>0.3683966097759201</v>
       </c>
       <c r="J62" t="n">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -3884,37 +3884,37 @@
         <v>192</v>
       </c>
       <c r="C63" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D63" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0625</v>
+        <v>0.453125</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.4272727272727272</v>
       </c>
       <c r="H63" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.4925699300699301</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.3274395329441201</v>
       </c>
       <c r="J63" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -3927,34 +3927,34 @@
         <v>192</v>
       </c>
       <c r="C64" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D64" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.078125</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3</v>
+        <v>0.2369791666666667</v>
       </c>
       <c r="H64" t="n">
-        <v>0.08241758241758242</v>
+        <v>0.5</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1293103448275862</v>
+        <v>0.3215547703180212</v>
       </c>
       <c r="J64" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -3970,34 +3970,34 @@
         <v>192</v>
       </c>
       <c r="C65" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D65" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G65" t="n">
-        <v>0.26</v>
+        <v>0.2473958333333333</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06842105263157895</v>
+        <v>0.5</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1083333333333334</v>
+        <v>0.3310104529616725</v>
       </c>
       <c r="J65" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -4013,37 +4013,37 @@
         <v>192</v>
       </c>
       <c r="C66" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D66" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="G66" t="n">
-        <v>0.75</v>
+        <v>0.5502645502645502</v>
       </c>
       <c r="H66" t="n">
-        <v>0.08290040897535095</v>
+        <v>0.5031502155410633</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1283569641367807</v>
+        <v>0.319327731092437</v>
       </c>
       <c r="J66" t="n">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4056,34 +4056,34 @@
         <v>192</v>
       </c>
       <c r="C67" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D67" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G67" t="n">
-        <v>0.22</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="H67" t="n">
-        <v>0.05978260869565218</v>
+        <v>0.5</v>
       </c>
       <c r="I67" t="n">
-        <v>0.09401709401709402</v>
+        <v>0.323943661971831</v>
       </c>
       <c r="J67" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -4099,34 +4099,34 @@
         <v>192</v>
       </c>
       <c r="C68" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D68" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2552083333333333</v>
       </c>
       <c r="H68" t="n">
-        <v>0.08163265306122448</v>
+        <v>0.5</v>
       </c>
       <c r="I68" t="n">
-        <v>0.125</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="J68" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -4142,34 +4142,34 @@
         <v>192</v>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D69" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="H69" t="n">
-        <v>0.07446808510638298</v>
+        <v>0.5</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="J69" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -4185,34 +4185,34 @@
         <v>192</v>
       </c>
       <c r="C70" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D70" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.2161458333333333</v>
       </c>
       <c r="H70" t="n">
-        <v>0.06024096385542169</v>
+        <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>0.09345794392523364</v>
+        <v>0.3018181818181818</v>
       </c>
       <c r="J70" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -4228,34 +4228,34 @@
         <v>192</v>
       </c>
       <c r="C71" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D71" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.484375</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.2421875</v>
       </c>
       <c r="H71" t="n">
-        <v>0.05913978494623656</v>
+        <v>0.5</v>
       </c>
       <c r="I71" t="n">
-        <v>0.09166666666666667</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="J71" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -4271,34 +4271,34 @@
         <v>192</v>
       </c>
       <c r="C72" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D72" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2630208333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>0.07920792079207921</v>
+        <v>0.5</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1259842519685039</v>
+        <v>0.3447098976109215</v>
       </c>
       <c r="J72" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -4314,34 +4314,34 @@
         <v>192</v>
       </c>
       <c r="C73" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D73" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.546875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2734375</v>
       </c>
       <c r="H73" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1068702290076336</v>
+        <v>0.3535353535353535</v>
       </c>
       <c r="J73" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -4357,34 +4357,34 @@
         <v>192</v>
       </c>
       <c r="C74" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D74" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="G74" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="H74" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.5</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="J74" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4400,34 +4400,34 @@
         <v>192</v>
       </c>
       <c r="C75" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D75" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.515625</v>
       </c>
       <c r="G75" t="n">
-        <v>0.25</v>
+        <v>0.2578125</v>
       </c>
       <c r="H75" t="n">
-        <v>0.06565656565656566</v>
+        <v>0.5</v>
       </c>
       <c r="I75" t="n">
-        <v>0.104</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="J75" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -4443,34 +4443,34 @@
         <v>192</v>
       </c>
       <c r="C76" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D76" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0625</v>
+        <v>0.515625</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2578125</v>
       </c>
       <c r="H76" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="J76" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -4486,37 +4486,37 @@
         <v>192</v>
       </c>
       <c r="C77" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D77" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.078125</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.7539267015706806</v>
       </c>
       <c r="H77" t="n">
-        <v>0.07731958762886598</v>
+        <v>0.5052631578947369</v>
       </c>
       <c r="I77" t="n">
-        <v>0.12</v>
+        <v>0.3472222222222223</v>
       </c>
       <c r="J77" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4529,34 +4529,34 @@
         <v>192</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D78" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.578125</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.2890625</v>
       </c>
       <c r="H78" t="n">
-        <v>0.07207207207207207</v>
+        <v>0.5</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1159420289855072</v>
+        <v>0.3663366336633663</v>
       </c>
       <c r="J78" t="n">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -4572,34 +4572,34 @@
         <v>192</v>
       </c>
       <c r="C79" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D79" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="H79" t="n">
-        <v>0.06914893617021277</v>
+        <v>0.5</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1074380165289256</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="J79" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -4615,34 +4615,34 @@
         <v>192</v>
       </c>
       <c r="C80" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D80" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.453125</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2</v>
+        <v>0.2265625</v>
       </c>
       <c r="H80" t="n">
-        <v>0.05747126436781609</v>
+        <v>0.5</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.3118279569892473</v>
       </c>
       <c r="J80" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -4658,34 +4658,34 @@
         <v>192</v>
       </c>
       <c r="C81" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D81" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="H81" t="n">
-        <v>0.05978260869565218</v>
+        <v>0.5</v>
       </c>
       <c r="I81" t="n">
-        <v>0.09243697478991597</v>
+        <v>0.323943661971831</v>
       </c>
       <c r="J81" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -4701,34 +4701,34 @@
         <v>192</v>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D82" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="G82" t="n">
-        <v>0.28</v>
+        <v>0.21875</v>
       </c>
       <c r="H82" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1284403669724771</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="J82" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -4744,34 +4744,34 @@
         <v>192</v>
       </c>
       <c r="C83" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D83" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.484375</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.243455497382199</v>
       </c>
       <c r="H83" t="n">
-        <v>0.07446808510638298</v>
+        <v>0.4946808510638298</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1186440677966102</v>
+        <v>0.3263157894736842</v>
       </c>
       <c r="J83" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -4787,34 +4787,34 @@
         <v>192</v>
       </c>
       <c r="C84" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D84" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.2657894736842105</v>
       </c>
       <c r="H84" t="n">
-        <v>0.07766990291262135</v>
+        <v>0.4902912621359223</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1230769230769231</v>
+        <v>0.3447098976109215</v>
       </c>
       <c r="J84" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -4830,34 +4830,34 @@
         <v>192</v>
       </c>
       <c r="C85" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D85" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1923076923076923</v>
+        <v>0.2786458333333333</v>
       </c>
       <c r="H85" t="n">
-        <v>0.04672897196261682</v>
+        <v>0.5</v>
       </c>
       <c r="I85" t="n">
-        <v>0.07518796992481203</v>
+        <v>0.3578595317725752</v>
       </c>
       <c r="J85" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -4873,37 +4873,37 @@
         <v>192</v>
       </c>
       <c r="C86" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D86" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="H86" t="n">
-        <v>0.07920792079207921</v>
+        <v>0.4955935153954956</v>
       </c>
       <c r="I86" t="n">
-        <v>0.125</v>
+        <v>0.352017608217168</v>
       </c>
       <c r="J86" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4916,37 +4916,37 @@
         <v>192</v>
       </c>
       <c r="C87" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D87" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.078125</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G87" t="n">
-        <v>0.3</v>
+        <v>0.5873015873015872</v>
       </c>
       <c r="H87" t="n">
-        <v>0.07731958762886598</v>
+        <v>0.505371676614216</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1229508196721312</v>
+        <v>0.3560724989296418</v>
       </c>
       <c r="J87" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4959,37 +4959,37 @@
         <v>192</v>
       </c>
       <c r="C88" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D88" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0625</v>
+        <v>0.53125</v>
       </c>
       <c r="G88" t="n">
-        <v>0.25</v>
+        <v>0.7643979057591623</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0594059405940594</v>
+        <v>0.5054945054945055</v>
       </c>
       <c r="I88" t="n">
-        <v>0.096</v>
+        <v>0.3567599761762953</v>
       </c>
       <c r="J88" t="n">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5002,34 +5002,34 @@
         <v>192</v>
       </c>
       <c r="C89" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D89" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0625</v>
+        <v>0.53125</v>
       </c>
       <c r="G89" t="n">
-        <v>0.25</v>
+        <v>0.2670157068062827</v>
       </c>
       <c r="H89" t="n">
-        <v>0.05825242718446602</v>
+        <v>0.4951456310679612</v>
       </c>
       <c r="I89" t="n">
-        <v>0.09448818897637797</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="J89" t="n">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -5045,34 +5045,34 @@
         <v>192</v>
       </c>
       <c r="C90" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D90" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G90" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="H90" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="I90" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.3424657534246575</v>
       </c>
       <c r="J90" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -5088,34 +5088,34 @@
         <v>192</v>
       </c>
       <c r="C91" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D91" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7748691099476439</v>
       </c>
       <c r="H91" t="n">
-        <v>0.07717569786535303</v>
+        <v>0.5057471264367817</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1285511363636364</v>
+        <v>0.3660933660933661</v>
       </c>
       <c r="J91" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="M91" t="n">
         <v>1</v>
@@ -5131,34 +5131,34 @@
         <v>192</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D92" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0625</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="G92" t="n">
-        <v>0.24</v>
+        <v>0.2760416666666667</v>
       </c>
       <c r="H92" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.5</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0916030534351145</v>
+        <v>0.3557046979865772</v>
       </c>
       <c r="J92" t="n">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -5174,37 +5174,37 @@
         <v>192</v>
       </c>
       <c r="C93" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D93" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.078125</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.5184210526315789</v>
       </c>
       <c r="H93" t="n">
-        <v>0.07281553398058252</v>
+        <v>0.5007636085960511</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1162790697674419</v>
+        <v>0.359111877883209</v>
       </c>
       <c r="J93" t="n">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5217,34 +5217,34 @@
         <v>192</v>
       </c>
       <c r="C94" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D94" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G94" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.2671957671957672</v>
       </c>
       <c r="H94" t="n">
-        <v>0.05288461538461538</v>
+        <v>0.4855769230769231</v>
       </c>
       <c r="I94" t="n">
-        <v>0.08593749999999999</v>
+        <v>0.3447098976109215</v>
       </c>
       <c r="J94" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -5260,37 +5260,37 @@
         <v>192</v>
       </c>
       <c r="C95" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D95" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3269230769230769</v>
+        <v>0.5</v>
       </c>
       <c r="H95" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0.139344262295082</v>
+        <v>0.3423719138004852</v>
       </c>
       <c r="J95" t="n">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5303,37 +5303,37 @@
         <v>192</v>
       </c>
       <c r="C96" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D96" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.078125</v>
+        <v>0.5</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0797872340425532</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="I96" t="n">
-        <v>0.1239669421487603</v>
+        <v>0.3509859154929578</v>
       </c>
       <c r="J96" t="n">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -5346,34 +5346,34 @@
         <v>192</v>
       </c>
       <c r="C97" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D97" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.078125</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G97" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2447916666666667</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0797872340425532</v>
+        <v>0.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.125</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="J97" t="n">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -5389,34 +5389,34 @@
         <v>192</v>
       </c>
       <c r="C98" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D98" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.46875</v>
       </c>
       <c r="G98" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.234375</v>
       </c>
       <c r="H98" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.5</v>
       </c>
       <c r="I98" t="n">
-        <v>0.07017543859649122</v>
+        <v>0.3191489361702128</v>
       </c>
       <c r="J98" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -5432,34 +5432,34 @@
         <v>192</v>
       </c>
       <c r="C99" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D99" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.078125</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3</v>
+        <v>0.2630208333333333</v>
       </c>
       <c r="H99" t="n">
-        <v>0.07425742574257425</v>
+        <v>0.5</v>
       </c>
       <c r="I99" t="n">
-        <v>0.119047619047619</v>
+        <v>0.3447098976109215</v>
       </c>
       <c r="J99" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -5475,34 +5475,34 @@
         <v>192</v>
       </c>
       <c r="C100" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D100" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G100" t="n">
-        <v>0.25</v>
+        <v>0.2329842931937173</v>
       </c>
       <c r="H100" t="n">
-        <v>0.07222222222222222</v>
+        <v>0.4944444444444445</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1120689655172414</v>
+        <v>0.3167259786476868</v>
       </c>
       <c r="J100" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -5518,34 +5518,34 @@
         <v>192</v>
       </c>
       <c r="C101" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D101" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2552083333333333</v>
       </c>
       <c r="H101" t="n">
-        <v>0.08163265306122448</v>
+        <v>0.5</v>
       </c>
       <c r="I101" t="n">
-        <v>0.126984126984127</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="J101" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1320</v>
+        <v>9515</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1286</v>
+        <v>9609</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -5651,16 +5651,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52</v>
+        <v>387</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>412</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -5670,13 +5670,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>404</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>396</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93</v>
+        <v>798</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>114</v>
+        <v>757</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -5708,16 +5708,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>102</v>
+        <v>801</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>118</v>
+        <v>792</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5727,16 +5727,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115</v>
+        <v>813</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>95</v>
+        <v>773</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>739</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>114</v>
+        <v>860</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -5765,16 +5765,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>767</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>97</v>
+        <v>826</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -5784,13 +5784,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>822</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>114</v>
+        <v>778</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -5803,13 +5803,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>803</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>109</v>
+        <v>796</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>126</v>
+        <v>812</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>99</v>
+        <v>788</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5841,13 +5841,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119</v>
+        <v>788</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>812</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>102</v>
+        <v>813</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>787</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>113</v>
+        <v>768</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>105</v>
+        <v>832</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
